--- a/output/laminas_comunales/comunal_m_movinterna_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (67,8); Independencia (69,4); Providencia (79,8); Calera de Tango (92,3); Santiago (82,0); Pirque (68,4); Vitacura (68,3); Estación Central (67,9); Ñuñoa (68,2).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_movinterna_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (67,8); Independencia (69,4); Providencia (79,8); Calera de Tango (92,3); Santiago (82,0); Pirque (68,4); Vitacura (68,3); Estación Central (67,9); Ñuñoa (68,2).</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (67,8); Independencia (69,4); Providencia (79,8); Calera de Tango (92,3); Santiago (82,0); Pirque (68,4); y 3 más.</t>
         </is>
       </c>
     </row>
